--- a/data/tools.xlsx
+++ b/data/tools.xlsx
@@ -1,50 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Inventory" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,85 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -216,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -250,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -284,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -419,193 +351,613 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H21"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Last Checked</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Item</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Condition</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Location</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Last Checked</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Hand trowel</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Hand tools</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" t="str">
+        <v>Bolo (Machete)</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Hand tools</v>
+      </c>
+      <c r="C2">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Tool shed</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE</t>
-        </is>
+      <c r="D2" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Watering can</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Irrigation</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="A3" t="str">
+        <v>Hoe</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Hand tools</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Hand trowel</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Hand tools</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Rake</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Hand tools</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Fair</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Two are missing a tooth</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Shovel</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Hand tools</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Grass cutter</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Power tools</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>units</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Needs fuel</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Water pump</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Power tools</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>unit</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Pump house</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Hose (50m)</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Irrigation</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="str">
+        <v>rolls</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Sprinkler head</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Irrigation</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Watering can</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Irrigation</v>
+      </c>
+      <c r="C11">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tool shed</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE: one has a leak</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Compost mix</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="D11" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Fair</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H11" t="str">
+        <v>One has a leak</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Pechay seeds</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Seeds</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" t="str">
+        <v>packs</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Storage room</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Expiry 2027</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Kangkong seeds</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Seeds</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13" t="str">
+        <v>packs</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Storage room</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Expiry 2027</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Tomato seedlings</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Seeds</v>
+      </c>
+      <c r="C14">
+        <v>50</v>
+      </c>
+      <c r="D14" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Nursery</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Ready for transplant</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Compost mix</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Consumables</v>
+      </c>
+      <c r="C15">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>sacks</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Storage room</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE</t>
-        </is>
+      <c r="D15" t="str">
+        <v>sacks</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Storage room</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Plastic mulch</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Consumables</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="str">
+        <v>rolls</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Storage room</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>String / tie wire</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Consumables</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17" t="str">
+        <v>rolls</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Storage room</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Gloves</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Safety</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+      <c r="D18" t="str">
+        <v>pairs</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Various sizes</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Rubber boots</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Safety</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19" t="str">
+        <v>pairs</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>First aid kit</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Safety</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="str">
+        <v>kits</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Check expiry dates</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Harvest crates</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Storage</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21" t="str">
+        <v>pcs</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Good</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Tool shed</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
+  </ignoredErrors>
 </worksheet>
 </file>